--- a/artfynd/A 5700-2024 artfynd.xlsx
+++ b/artfynd/A 5700-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5700-2024 artfynd.xlsx
+++ b/artfynd/A 5700-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3933953</v>
+        <v>95246</v>
       </c>
       <c r="B2" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Elinge båtmansboställe, 0,1 km O-ut, Upl</t>
+          <t>Elinge båtmansboställe, 0,1 km NO-ut, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655350.0659466106</v>
+        <v>655372</v>
       </c>
       <c r="R2" t="n">
-        <v>6695534.140636303</v>
+        <v>6695592</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-05-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-05-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,6 +760,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>ved</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -789,6 +779,536 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2925620</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Elinge båtmansboställe, 0,1 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>655393</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6695582</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2010-08-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2010-08-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2925621</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Elinge båtmansboställe, 0,1 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>655372</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6695592</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2010-08-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2010-08-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3932212</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Elinge båtmansboställe, 0,1 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>655372</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6695592</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2010-08-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2010-08-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3933953</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Elinge båtmansboställe, 0,1 km O-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>655350</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6695534</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2011-05-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2011-05-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4944894</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Elinge båtmansboställe, 0,1 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>655393</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6695582</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2010-08-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2010-08-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>

--- a/artfynd/A 5700-2024 artfynd.xlsx
+++ b/artfynd/A 5700-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95246</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2925620</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2925621</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3932212</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3933953</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,8 +1343,21 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4944894</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>